--- a/cds_files/Utah_CDS_2024-2025.xlsx
+++ b/cds_files/Utah_CDS_2024-2025.xlsx
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28064</v>
+        <v>27264</v>
       </c>
     </row>
     <row r="5">

--- a/cds_files/Utah_CDS_2024-2025.xlsx
+++ b/cds_files/Utah_CDS_2024-2025.xlsx
@@ -499,7 +499,7 @@
         <v>0.64</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.36</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5">
